--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="D2" t="n">
-        <v>81.51000000000001</v>
+        <v>84.61</v>
       </c>
       <c r="E2" t="n">
-        <v>81.51000000000001</v>
+        <v>84.61</v>
       </c>
       <c r="F2" t="n">
-        <v>13.64</v>
+        <v>17.91</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>9.880000000000001</v>
+        <v>6.36</v>
       </c>
       <c r="E3" t="n">
-        <v>91.39</v>
+        <v>90.97</v>
       </c>
       <c r="F3" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="G3" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -535,16 +535,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="D4" t="n">
-        <v>4.69</v>
+        <v>4.28</v>
       </c>
       <c r="E4" t="n">
-        <v>96.08</v>
+        <v>95.25</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -565,16 +565,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.23</v>
+        <v>0.31</v>
       </c>
       <c r="D5" t="n">
-        <v>2.43</v>
+        <v>3.6</v>
       </c>
       <c r="E5" t="n">
-        <v>98.51000000000001</v>
+        <v>98.84999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -595,16 +595,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.49</v>
+        <v>1.15</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>

--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
+++ b/results/ref_threshold_sensitivity/tables/SumRel_rda_axes_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,16 +475,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.39</v>
+        <v>2.56</v>
       </c>
       <c r="D2" t="n">
-        <v>84.61</v>
+        <v>57.6</v>
       </c>
       <c r="E2" t="n">
-        <v>84.61</v>
+        <v>57.6</v>
       </c>
       <c r="F2" t="n">
-        <v>17.91</v>
+        <v>7.13</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -505,19 +505,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="D3" t="n">
-        <v>6.36</v>
+        <v>20.45</v>
       </c>
       <c r="E3" t="n">
-        <v>90.97</v>
+        <v>78.05</v>
       </c>
       <c r="F3" t="n">
-        <v>1.35</v>
+        <v>2.53</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="D4" t="n">
-        <v>4.28</v>
+        <v>11.05</v>
       </c>
       <c r="E4" t="n">
-        <v>95.25</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.91</v>
+        <v>1.37</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -565,19 +565,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>98.84999999999999</v>
+        <v>98.06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.15</v>
+        <v>1.94</v>
       </c>
       <c r="E6" t="n">
         <v>100</v>
